--- a/sources.xlsx
+++ b/sources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://monashuni-my.sharepoint.com/personal/ofaz0002_student_monash_edu/Documents/2026/S1-FIT2179/A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_F25DC773A252ABDACC10486069DC6CD45ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C20BAEFB-EA47-4E43-811A-818C193B7646}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_F25DC773A252ABDACC10486069DC6CD45ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E6B0D6C-E990-4F74-BF2F-65034FC04160}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="-11160" windowWidth="15675" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34740" yWindow="5730" windowWidth="44820" windowHeight="22515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>https://discover.data.vic.gov.au/dataset/bicycle-infrastructure-network</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>Bicycle volume and speed - historical - DoT Bike Site Number Listing - Victorian Government Data Vic</t>
+  </si>
+  <si>
+    <t>Bicycle Volume and Speed - Bike Site Number Listing - Open Data - Transport Victoria</t>
   </si>
 </sst>
 </file>
@@ -127,6 +130,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -392,19 +399,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -415,7 +422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -426,7 +433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -437,7 +444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -448,7 +455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -459,7 +466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -470,12 +477,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -486,8 +498,9 @@
     <hyperlink ref="B7" r:id="rId4" display="https://discover.data.vic.gov.au/dataset/bicycle-volume-and-speed" xr:uid="{60C2DC64-F26A-4386-A661-9CF11C01DA67}"/>
     <hyperlink ref="B3" r:id="rId5" xr:uid="{40E02233-2BFD-492F-86AC-C754C218976C}"/>
     <hyperlink ref="B8" r:id="rId6" display="https://discover.data.vic.gov.au/dataset/bicycle-volume-and-speed-historical/resource/f4f6fb31-982f-4182-ac0c-0fcd52c58eeb?view_id=bf4158f8-35b5-40e6-abc6-d73a24f56611" xr:uid="{BBA91F5C-B06B-4497-B91C-975B19878FDC}"/>
+    <hyperlink ref="B9" r:id="rId7" display="https://opendata.transport.vic.gov.au/dataset/bicycle-volume-and-speed/resource/7f25d12e-99a6-48b4-97ff-af6554fa7118" xr:uid="{3C540FDA-9030-42E9-B72C-A87776CD3FF0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="119" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId7"/>
+  <pageSetup paperSize="119" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId8"/>
 </worksheet>
 </file>